--- a/quotations/seoul-night-market-quotation.xlsx
+++ b/quotations/seoul-night-market-quotation.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="¥#,##0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,19 +39,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001A1A2E"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C0392B"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001E8449"/>
     </font>
     <font>
       <b val="1"/>
@@ -63,15 +55,20 @@
       <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+    </font>
+    <font>
       <color rgb="00888888"/>
       <sz val="10"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000000FF"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,7 +82,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFCD00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF8DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,34 +135,34 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -524,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -542,7 +549,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>首尔夜市 · 品牌产品配置报价表（数量×单价自动计算）</t>
+          <t>首尔夜市 · 品牌产品配置报价表（2026-09-09勾选版）</t>
         </is>
       </c>
     </row>
@@ -598,512 +605,588 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>一、软件产品</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>门店管理系统（POS）</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="6" t="n">
         <v>1780</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="6" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="C4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>商家小程序</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>会员管理</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="6" t="n">
         <v>1440</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="C6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>外卖聚合</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="6" t="n">
         <v>290</v>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>KDS智能厨房</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="6" t="n">
         <v>750</v>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>美团点评排队</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="6" t="n">
         <v>520</v>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>智能叫号</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="6" t="n">
         <v>380</v>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>数电发票</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="6" t="n">
         <v>1088</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="C11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>门店进销存</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="6" t="n">
         <v>750</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="C12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>副收银系统</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B13" s="6" t="n">
         <v>660</v>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>门店代运维</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>1600</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="C14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>软件小计</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,C4:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,D4:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,E4:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,F4:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,G4:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,H4:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,I4:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11">
+        <f>SUMPRODUCT($B$4:$B$14,J4:J14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>二、硬件设备</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>P2平板</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B17" s="6" t="n">
         <v>1398</v>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>S4mini Pro</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B18" s="6" t="n">
         <v>1698</v>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>S5 Pro</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B19" s="6" t="n">
         <v>1398</v>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>S5S Pro</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B20" s="6" t="n">
         <v>1698</v>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>80N打印机</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B21" s="6" t="n">
         <v>269</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H21" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>LP2标签打印机</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B22" s="6" t="n">
         <v>429</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>原价小计</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,C3:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,D3:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,E3:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,F3:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,G3:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,H3:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,I3:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="8">
-        <f>SUMPRODUCT($B$3:$B$19,J3:J19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>折后小计</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>折扣率→</t>
-        </is>
-      </c>
-      <c r="C21" s="10">
-        <f>ROUND(C20*$C$24,0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="10">
-        <f>ROUND(D20*$C$24,0)</f>
-        <v/>
-      </c>
-      <c r="E21" s="10">
-        <f>ROUND(E20*$C$24,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
-        <f>ROUND(F20*$C$24,0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="10">
-        <f>ROUND(G20*$C$24,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="10">
-        <f>ROUND(H20*$C$24,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="10">
-        <f>ROUND(I20*$C$24,0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="10">
-        <f>ROUND(J20*$C$24,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>折后总计（已选品牌合计）</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="12">
-        <f>SUM(C21:J21)</f>
+      <c r="C22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>硬件小计</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,C17:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,D17:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,E17:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,F17:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,G17:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,H17:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,I17:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="11">
+        <f>SUMPRODUCT($B$17:$B$22,J17:J22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>折扣率(可改)</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>原价合计（软件+硬件）</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="13">
+        <f>C15+C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="13">
+        <f>D15+D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="13">
+        <f>E15+E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="13">
+        <f>F15+F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="13">
+        <f>G15+G23</f>
+        <v/>
+      </c>
+      <c r="H24" s="13">
+        <f>H15+H23</f>
+        <v/>
+      </c>
+      <c r="I24" s="13">
+        <f>I15+I23</f>
+        <v/>
+      </c>
+      <c r="J24" s="13">
+        <f>J15+J23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>折后价（手动填写）</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>说明：表格内数字为数量（软件=1套，硬件=台数）；黄色底=已勾选；空白=未勾选，可自行填写数量，小计自动重算。Twozzim / Farm Market 未勾选任何产品。</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>折后总计（8品牌）</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="16">
+        <f>SUM(C25:J25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>说明：数字=数量（软件1套、硬件台数），黄底=已勾选；空白格可填数量自动计入小计。黄色折后价行由你手动填写，折后总计自动求和。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A26:J26"/>
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A28:J28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
